--- a/data/trans_camb/P1418-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1418-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,57</t>
+          <t>-0,74</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,14</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -0,12</t>
+          <t>-4,2; -0,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 0,2</t>
+          <t>-4,02; 0,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 1,66</t>
+          <t>-2,93; 1,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 4,75</t>
+          <t>-1,83; 4,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 2,28</t>
+          <t>-3,96; 1,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,55</t>
+          <t>-2,28; 3,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,65</t>
+          <t>-2,41; 1,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 0,64</t>
+          <t>-3,07; 0,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,0</t>
+          <t>-1,72; 1,81</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-10,83%</t>
+          <t>-14,15%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-67,13; -0,27</t>
+          <t>-66,08; -6,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,0; 6,53</t>
+          <t>-63,06; 4,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,15; 40,97</t>
+          <t>-45,04; 35,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 66,03</t>
+          <t>-19,03; 61,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 33,29</t>
+          <t>-39,45; 26,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 51,03</t>
+          <t>-21,21; 47,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,77; 29,2</t>
+          <t>-29,97; 24,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,24; 11,41</t>
+          <t>-38,87; 10,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 34,25</t>
+          <t>-21,58; 30,54</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,56</t>
+          <t>-1,71</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>-1,24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,15</t>
+          <t>-1,46</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; -0,16</t>
+          <t>-3,84; -0,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,2; -1,57</t>
+          <t>-5,0; -1,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -0,7</t>
+          <t>-3,54; 0,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 3,27</t>
+          <t>-2,25; 3,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,07; -0,83</t>
+          <t>-6,19; -0,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 1,3</t>
+          <t>-3,41; 1,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,02</t>
+          <t>-2,42; 1,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; -1,76</t>
+          <t>-4,87; -1,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,38; -0,61</t>
+          <t>-3,08; 0,03</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-45,3%</t>
+          <t>-30,3%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-11,64%</t>
+          <t>-12,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-28,03%</t>
+          <t>-19,05%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,36; -0,55</t>
+          <t>-57,28; -1,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-74,04; -32,44</t>
+          <t>-74,38; -31,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,42; -15,12</t>
+          <t>-51,3; 8,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 39,5</t>
+          <t>-21,37; 41,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,46; -10,27</t>
+          <t>-54,87; -10,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 16,37</t>
+          <t>-30,94; 13,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,17; 15,26</t>
+          <t>-28,35; 15,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,97; -25,82</t>
+          <t>-56,24; -25,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-53,66; -10,07</t>
+          <t>-35,14; 0,39</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-0,75</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,13</t>
+          <t>-3,18</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,82</t>
+          <t>-1,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,27</t>
+          <t>-4,24; 0,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; -0,78</t>
+          <t>-5,16; -0,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 1,66</t>
+          <t>-3,06; 1,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,79; -0,56</t>
+          <t>-6,79; -0,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,84; -0,64</t>
+          <t>-6,94; -0,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,99; -1,82</t>
+          <t>-6,12; -0,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,66; -0,87</t>
+          <t>-4,73; -1,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,26; -1,26</t>
+          <t>-5,38; -1,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; -0,71</t>
+          <t>-3,87; -0,12</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-14,16%</t>
+          <t>-14,43%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-45,13%</t>
+          <t>-28,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-34,0%</t>
+          <t>-23,73%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-66,61; 10,29</t>
+          <t>-68,32; 16,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-74,91; -15,2</t>
+          <t>-76,12; -15,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,46; 47,71</t>
+          <t>-47,32; 40,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-51,54; -5,78</t>
+          <t>-52,18; -7,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,95; -6,43</t>
+          <t>-53,04; -6,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-74,03; -18,87</t>
+          <t>-46,11; -4,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,96; -11,43</t>
+          <t>-50,02; -13,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,89; -17,05</t>
+          <t>-56,62; -20,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,22; -10,99</t>
+          <t>-40,12; -1,16</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,2</t>
+          <t>-1,42</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,77</t>
+          <t>-1,58</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,42</t>
+          <t>-1,48</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,96; -1,27</t>
+          <t>-4,76; -1,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,68; -2,34</t>
+          <t>-5,57; -2,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,86</t>
+          <t>-3,26; 0,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,29</t>
+          <t>-3,06; 2,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,17; -0,9</t>
+          <t>-5,99; -1,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 1,19</t>
+          <t>-4,1; 0,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,1</t>
+          <t>-3,31; 0,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,12; -2,07</t>
+          <t>-5,29; -2,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,43</t>
+          <t>-3,18; 0,13</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-21,29%</t>
+          <t>-25,27%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-16,26%</t>
+          <t>-14,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-16,95%</t>
+          <t>-17,62%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-73,01; -26,04</t>
+          <t>-72,89; -22,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-82,76; -45,35</t>
+          <t>-81,71; -42,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,55; 18,56</t>
+          <t>-47,61; 13,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 24,32</t>
+          <t>-24,6; 25,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,01; -8,76</t>
+          <t>-49,32; -9,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 13,18</t>
+          <t>-32,93; 7,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-35,69; 1,15</t>
+          <t>-35,45; 0,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-56,34; -27,33</t>
+          <t>-57,48; -29,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 6,03</t>
+          <t>-33,47; 1,83</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,44</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,87</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,63</t>
+          <t>-1,25</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -1,4</t>
+          <t>-3,32; -1,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -2,1</t>
+          <t>-4,01; -2,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,61; -0,4</t>
+          <t>-2,27; -0,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,29</t>
+          <t>-1,98; 1,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -1,57</t>
+          <t>-4,53; -1,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; -0,41</t>
+          <t>-2,68; -0,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,21; -0,49</t>
+          <t>-2,23; -0,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,9; -2,21</t>
+          <t>-3,87; -2,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,65; -0,71</t>
+          <t>-2,08; -0,38</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-26,43%</t>
+          <t>-22,42%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-18,4%</t>
+          <t>-13,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-20,81%</t>
+          <t>-15,92%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-54,87; -27,79</t>
+          <t>-55,75; -27,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-65,98; -42,71</t>
+          <t>-66,86; -43,06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-44,33; -8,25</t>
+          <t>-38,04; -5,53</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 14,11</t>
+          <t>-17,69; 10,78</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,81; -15,61</t>
+          <t>-41,07; -17,04</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-32,99; -4,63</t>
+          <t>-24,06; -0,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-26,54; -6,29</t>
+          <t>-26,72; -4,96</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-45,74; -29,68</t>
+          <t>-46,79; -29,05</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-32,45; -10,04</t>
+          <t>-25,02; -5,12</t>
         </is>
       </c>
     </row>
